--- a/ipo-analysis/companies/sfc-environmental-technologies-ltd/SFC_ENVIRONMENTAL_TECHNO_03_Valuation.xlsx
+++ b/ipo-analysis/companies/sfc-environmental-technologies-ltd/SFC_ENVIRONMENTAL_TECHNO_03_Valuation.xlsx
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="C14" s="15" t="n">
-        <v>1.23075</v>
+        <v>1.568275</v>
       </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="C15" s="15" t="n">
-        <v>533</v>
+        <v>313</v>
       </c>
       <c r="D15" s="21" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="C16" s="15" t="n">
-        <v>533</v>
+        <v>330</v>
       </c>
       <c r="D16" s="21" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="C18" s="15" t="n">
-        <v>117.13</v>
+        <v>117.145</v>
       </c>
       <c r="D18" s="21" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="C25" s="15" t="n">
-        <v>697.8579999999999</v>
+        <v>803.629</v>
       </c>
       <c r="D25" s="21" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="C26" s="15" t="n">
-        <v>657.495</v>
+        <v>697.8579999999999</v>
       </c>
       <c r="D26" s="21" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="C27" s="15" t="n">
-        <v>207.48</v>
+        <v>235.812</v>
       </c>
       <c r="D27" s="21" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C28" s="15" t="n">
-        <v>17.841</v>
+        <v>27.846</v>
       </c>
       <c r="D28" s="21" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="C29" s="15" t="n">
-        <v>144.06</v>
+        <v>154.361</v>
       </c>
       <c r="D29" s="21" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="C30" s="15" t="n">
-        <v>648.682</v>
+        <v>777.465</v>
       </c>
       <c r="D30" s="21" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="C31" s="15" t="n">
-        <v>-52.345</v>
+        <v>92.477</v>
       </c>
       <c r="D31" s="21" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="C32" s="15" t="n">
-        <v>491.784</v>
+        <v>615.044</v>
       </c>
       <c r="D32" s="21" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="C33" s="15" t="n">
-        <v>392.208</v>
+        <v>491.784</v>
       </c>
       <c r="D33" s="21" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="C34" s="15" t="n">
-        <v>30.95</v>
+        <v>16.28</v>
       </c>
       <c r="D34" s="21" t="inlineStr">
         <is>
@@ -2148,17 +2148,17 @@
         <v/>
       </c>
       <c r="E67" s="16" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="F67" s="16" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="G67" s="16" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H67" s="20" t="inlineStr">
         <is>
-          <t>Revenue CAGR 15.91% FY23-25 (Rs 519.45 cr -&gt; Rs 697.86 cr), but only +6.1% in FY25 as WWT revenue fell from Rs 524.44 cr to Rs 469.21 cr and the WWT order book from Rs 656.45 cr to Rs 459.75 cr (pp. 49, 449-450). Total order book Rs 1,267.50 cr at 15-Aug-2025 (1.8x FY25 revenue) after Rs 501.70 cr of CBG plant orders and the first WRR order (pp. 49, 262). Neutral 12-15% as the CBG EPC orders execute; Bear assumes WWT stays soft; Bull adds DuPont-led WRR growth (p. 261).</t>
+          <t>Revenue Rs 657.50 / 697.86 / 803.63 cr FY24-26 (+6.1%, +15.2%); WWT segment Rs 524.44 / 469.21 / 542.76 cr (p. 501). Total order book Rs 1,574.52 cr at Mar-26 (2.0x FY26 revenue) and Rs 1,570.07 cr at Jun-26 (p. 188); Q1 FY27 revenue Rs 133.94 cr vs Rs 67.79 cr (Q1 is seasonally small). Neutral 18% then easing to 10% as the CBG EPC orders execute; Bear 6-8%; Bull 25% then 12%.</t>
         </is>
       </c>
     </row>
@@ -2173,13 +2173,13 @@
         <v/>
       </c>
       <c r="E68" s="16" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="F68" s="16" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="G68" s="16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="H68" s="20" t="inlineStr">
         <is>
@@ -2201,10 +2201,10 @@
         <v>0.08</v>
       </c>
       <c r="F69" s="16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="G69" s="16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="H69" s="20" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>0.12</v>
       </c>
       <c r="G70" s="16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="H70" s="20" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="H72" s="20" t="inlineStr">
         <is>
-          <t>Operating EBITDA (issuer KPI, net of other income) Rs 124.07 / 193.25 / 207.48 cr = 23.89% / 29.39% / 29.73% (p. 170). WWT segment margin 34.7% in FY25; SWT 31.0%; automation 10.4% (p. 450). Neutral 28%, a little below FY25 as lower-margin CBG EPC work grows; Bear 24% (FY23 level); Bull holds 30%.</t>
+          <t>Operating EBITDA (issuer KPI) Rs 193.25 / 207.48 / 235.81 cr = 29.39% / 29.73% / 29.34% (p. 188). Neutral 28% as lower-margin CBG EPC work grows; Bear 24%; Bull 30%.</t>
         </is>
       </c>
     </row>
@@ -2298,17 +2298,17 @@
         <v/>
       </c>
       <c r="E73" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F73" s="16" t="n">
         <v>0.7</v>
       </c>
-      <c r="F73" s="16" t="n">
+      <c r="G73" s="16" t="n">
         <v>0.6</v>
       </c>
-      <c r="G73" s="16" t="n">
-        <v>0.5</v>
-      </c>
       <c r="H73" s="20" t="inlineStr">
         <is>
-          <t>Trade working capital (receivables incl. non-current + inventory - payables) 39.3% / 59.7% / 70.5% of revenue FY23-25 (pp. 362-363); the issuer's own working-capital ratio is 27.8% / 39.9% / 63.5% (p. 34). Neutral 60% assumes part of the FY24-25 build reverses as receivable days come off 262; Bear holds 70%; Bull 50%.</t>
+          <t>Trade working capital (receivables incl. non-current + inventory - payables) 59.7% / 70.5% / 76.5% of revenue FY24-26 (p. 411). Neutral 70%, assuming partial normalisation with the Rs 74.92 cr working-capital object; Bear 80%; Bull 60%.</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="H74" s="20" t="inlineStr">
         <is>
-          <t>ROCE 28.57% / 28.56% / 29.29% FY23-25 (p. 170), with net cash. Neutral terminal ROIC 20% allows for a heavier working-capital and SWT asset base.</t>
+          <t>ROCE 28.56% / 29.29% / 22.21% FY24-26 (p. 188). Neutral terminal ROIC 20%.</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>Energy and environment solutions incl. water and waste - issuer's peer, p. 168</t>
+          <t>Energy and environment solutions incl. water and waste - issuer's peer, p. 186</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>3273.4</v>
+        <v>3325.75</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -3326,12 +3326,14 @@
       <c r="I5" s="15" t="n"/>
       <c r="J5" s="15" t="n"/>
       <c r="K5" s="15" t="n">
-        <v>56.31</v>
+        <v>63.94</v>
       </c>
       <c r="L5" s="15" t="n">
-        <v>438.17</v>
-      </c>
-      <c r="M5" s="16" t="n"/>
+        <v>492.55</v>
+      </c>
+      <c r="M5" s="16" t="n">
+        <v>0.0294</v>
+      </c>
       <c r="N5" s="13">
         <f>IF(F5="","",F5*G5)</f>
         <v/>
@@ -3369,12 +3371,12 @@
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>Bio-energy, CBG and water / wastewater - issuer's peer, p. 168</t>
+          <t>Bio-energy and water - issuer's peer, p. 186; excluded: FY26 EPS Rs 1.30 makes the P/E (220.8x) not meaningful</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -3383,7 +3385,7 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>411.7</v>
+        <v>287</v>
       </c>
       <c r="G6" s="15" t="n">
         <v>1</v>
@@ -3392,12 +3394,14 @@
       <c r="I6" s="15" t="n"/>
       <c r="J6" s="15" t="n"/>
       <c r="K6" s="15" t="n">
-        <v>11.91</v>
+        <v>1.3</v>
       </c>
       <c r="L6" s="15" t="n">
-        <v>75.17</v>
-      </c>
-      <c r="M6" s="16" t="n"/>
+        <v>71.22</v>
+      </c>
+      <c r="M6" s="16" t="n">
+        <v>-0.0186</v>
+      </c>
       <c r="N6" s="13">
         <f>IF(F6="","",F6*G6)</f>
         <v/>
@@ -3440,7 +3444,7 @@
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>Water and wastewater treatment - issuer's peer, p. 168</t>
+          <t>Water and wastewater treatment - issuer's peer, p. 186</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -3449,7 +3453,7 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>431.45</v>
+        <v>377.2</v>
       </c>
       <c r="G7" s="15" t="n">
         <v>1</v>
@@ -3458,12 +3462,14 @@
       <c r="I7" s="15" t="n"/>
       <c r="J7" s="15" t="n"/>
       <c r="K7" s="15" t="n">
-        <v>17.53</v>
+        <v>12.03</v>
       </c>
       <c r="L7" s="15" t="n">
-        <v>82.36</v>
-      </c>
-      <c r="M7" s="16" t="n"/>
+        <v>91.3</v>
+      </c>
+      <c r="M7" s="16" t="n">
+        <v>0.0649</v>
+      </c>
       <c r="N7" s="13">
         <f>IF(F7="","",F7*G7)</f>
         <v/>
